--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2025/202511/AllSymbols_P&L_20251107.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2025/202511/AllSymbols_P&L_20251107.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="163">
   <si>
     <t>Symbol</t>
   </si>
@@ -286,7 +286,13 @@
     <t>EBND</t>
   </si>
   <si>
+    <t>EMLC</t>
+  </si>
+  <si>
     <t>IEF</t>
+  </si>
+  <si>
+    <t>SGOV</t>
   </si>
   <si>
     <t>SHYG</t>
@@ -854,7 +860,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I163"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -903,10 +909,10 @@
         <v>3674880</v>
       </c>
       <c r="F2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H2">
         <v>0.1286</v>
@@ -932,10 +938,10 @@
         <v>13933920</v>
       </c>
       <c r="F3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H3">
         <v>0.1286</v>
@@ -961,10 +967,10 @@
         <v>12438450</v>
       </c>
       <c r="F4" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H4">
         <v>0.1286</v>
@@ -990,10 +996,10 @@
         <v>6772950</v>
       </c>
       <c r="F5" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G5" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H5">
         <v>0.1286</v>
@@ -1019,10 +1025,10 @@
         <v>1900800</v>
       </c>
       <c r="F6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H6">
         <v>0.1286</v>
@@ -1048,10 +1054,10 @@
         <v>3889620</v>
       </c>
       <c r="F7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H7">
         <v>0.1286</v>
@@ -1077,10 +1083,10 @@
         <v>1725270</v>
       </c>
       <c r="F8" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G8" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H8">
         <v>0.1286</v>
@@ -1106,10 +1112,10 @@
         <v>4602420</v>
       </c>
       <c r="F9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H9">
         <v>0.1286</v>
@@ -1135,10 +1141,10 @@
         <v>16646400</v>
       </c>
       <c r="F10" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G10" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H10">
         <v>0.1286</v>
@@ -1164,10 +1170,10 @@
         <v>4735657</v>
       </c>
       <c r="F11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H11">
         <v>0.1286</v>
@@ -1193,10 +1199,10 @@
         <v>6366900</v>
       </c>
       <c r="F12" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G12" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H12">
         <v>0.1286</v>
@@ -1222,10 +1228,10 @@
         <v>29530540</v>
       </c>
       <c r="F13" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G13" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H13">
         <v>0.1286</v>
@@ -1251,10 +1257,10 @@
         <v>9879060</v>
       </c>
       <c r="F14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H14">
         <v>0.1286</v>
@@ -1280,10 +1286,10 @@
         <v>31319600</v>
       </c>
       <c r="F15" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G15" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H15">
         <v>0.1286</v>
@@ -1309,10 +1315,10 @@
         <v>12543080</v>
       </c>
       <c r="F16" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G16" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H16">
         <v>0.1286</v>
@@ -1338,10 +1344,10 @@
         <v>81940100</v>
       </c>
       <c r="F17" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G17" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H17">
         <v>0.0065</v>
@@ -1367,10 +1373,10 @@
         <v>86480500</v>
       </c>
       <c r="F18" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G18" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H18">
         <v>0.0065</v>
@@ -1396,10 +1402,10 @@
         <v>5820840</v>
       </c>
       <c r="F19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H19">
         <v>0.1286</v>
@@ -1425,10 +1431,10 @@
         <v>2753400</v>
       </c>
       <c r="F20" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G20" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H20">
         <v>0.1286</v>
@@ -1454,10 +1460,10 @@
         <v>6511880</v>
       </c>
       <c r="F21" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G21" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H21">
         <v>0.1286</v>
@@ -1483,10 +1489,10 @@
         <v>5273725</v>
       </c>
       <c r="F22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G22" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H22">
         <v>0.1286</v>
@@ -1512,10 +1518,10 @@
         <v>5481144</v>
       </c>
       <c r="F23" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G23" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H23">
         <v>0.7685</v>
@@ -1541,10 +1547,10 @@
         <v>5906.34</v>
       </c>
       <c r="F24" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G24" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -1570,10 +1576,10 @@
         <v>17358.04</v>
       </c>
       <c r="F25" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G25" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -1599,10 +1605,10 @@
         <v>8307398.5</v>
       </c>
       <c r="F26" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -1628,10 +1634,10 @@
         <v>363933.6</v>
       </c>
       <c r="F27" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G27" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -1657,10 +1663,10 @@
         <v>2538390</v>
       </c>
       <c r="F28" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G28" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H28">
         <v>1</v>
@@ -1686,10 +1692,10 @@
         <v>751939.02</v>
       </c>
       <c r="F29" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G29" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -1715,10 +1721,10 @@
         <v>831.7</v>
       </c>
       <c r="F30" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G30" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -1744,10 +1750,10 @@
         <v>140805</v>
       </c>
       <c r="F31" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G31" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -1773,10 +1779,10 @@
         <v>1852168</v>
       </c>
       <c r="F32" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G32" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H32">
         <v>0.7685</v>
@@ -1802,10 +1808,10 @@
         <v>199356.5</v>
       </c>
       <c r="F33" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G33" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -1831,10 +1837,10 @@
         <v>282940</v>
       </c>
       <c r="F34" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G34" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H34">
         <v>0.7685</v>
@@ -1860,10 +1866,10 @@
         <v>972262.5</v>
       </c>
       <c r="F35" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G35" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -1889,10 +1895,10 @@
         <v>1468323.83</v>
       </c>
       <c r="F36" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G36" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -1918,10 +1924,10 @@
         <v>394012.5</v>
       </c>
       <c r="F37" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G37" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -1947,10 +1953,10 @@
         <v>171572.7</v>
       </c>
       <c r="F38" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G38" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -1976,10 +1982,10 @@
         <v>1959.66</v>
       </c>
       <c r="F39" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G39" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -2005,10 +2011,10 @@
         <v>2159.24</v>
       </c>
       <c r="F40" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G40" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -2034,10 +2040,10 @@
         <v>5330.25</v>
       </c>
       <c r="F41" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G41" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -2063,10 +2069,10 @@
         <v>663661.02</v>
       </c>
       <c r="F42" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G42" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -2092,10 +2098,10 @@
         <v>474826.26</v>
       </c>
       <c r="F43" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G43" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -2121,10 +2127,10 @@
         <v>54980</v>
       </c>
       <c r="F44" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G44" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H44">
         <v>0.7685</v>
@@ -2150,10 +2156,10 @@
         <v>8223.32</v>
       </c>
       <c r="F45" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G45" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H45">
         <v>1</v>
@@ -2179,10 +2185,10 @@
         <v>3742.32</v>
       </c>
       <c r="F46" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G46" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -2208,10 +2214,10 @@
         <v>5254.2</v>
       </c>
       <c r="F47" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G47" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -2237,10 +2243,10 @@
         <v>154.35</v>
       </c>
       <c r="F48" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G48" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -2266,10 +2272,10 @@
         <v>1610439.82</v>
       </c>
       <c r="F49" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G49" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -2295,10 +2301,10 @@
         <v>377.2</v>
       </c>
       <c r="F50" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G50" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -2324,10 +2330,10 @@
         <v>235024.35</v>
       </c>
       <c r="F51" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G51" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -2353,10 +2359,10 @@
         <v>315088.11</v>
       </c>
       <c r="F52" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G52" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -2382,10 +2388,10 @@
         <v>574638.86</v>
       </c>
       <c r="F53" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G53" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -2411,10 +2417,10 @@
         <v>258.4</v>
       </c>
       <c r="F54" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G54" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -2440,10 +2446,10 @@
         <v>1009381.95</v>
       </c>
       <c r="F55" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G55" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -2469,10 +2475,10 @@
         <v>43134.75</v>
       </c>
       <c r="F56" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G56" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -2498,10 +2504,10 @@
         <v>27833.25</v>
       </c>
       <c r="F57" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G57" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -2527,10 +2533,10 @@
         <v>114892.5</v>
       </c>
       <c r="F58" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G58" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -2556,10 +2562,10 @@
         <v>316178</v>
       </c>
       <c r="F59" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G59" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -2585,10 +2591,10 @@
         <v>2587998.24</v>
       </c>
       <c r="F60" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G60" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -2602,28 +2608,28 @@
         <v>49</v>
       </c>
       <c r="B61">
-        <v>2000</v>
+        <v>2120</v>
       </c>
       <c r="C61">
         <v>314.21</v>
       </c>
       <c r="D61">
-        <v>1580</v>
+        <v>1674.8</v>
       </c>
       <c r="E61">
-        <v>628420</v>
+        <v>666125.2</v>
       </c>
       <c r="F61" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G61" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61">
-        <v>628420</v>
+        <v>666125.2</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -2643,10 +2649,10 @@
         <v>1808702.46</v>
       </c>
       <c r="F62" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G62" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H62">
         <v>1</v>
@@ -2672,10 +2678,10 @@
         <v>47628.8</v>
       </c>
       <c r="F63" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G63" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -2701,10 +2707,10 @@
         <v>693277.5</v>
       </c>
       <c r="F64" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -2730,10 +2736,10 @@
         <v>5355140</v>
       </c>
       <c r="F65" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G65" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H65">
         <v>0.7685</v>
@@ -2759,10 +2765,10 @@
         <v>160253.6</v>
       </c>
       <c r="F66" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G66" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H66">
         <v>1</v>
@@ -2788,10 +2794,10 @@
         <v>527400</v>
       </c>
       <c r="F67" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G67" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -2817,10 +2823,10 @@
         <v>1360071.6</v>
       </c>
       <c r="F68" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G68" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -2846,10 +2852,10 @@
         <v>775015.4300000001</v>
       </c>
       <c r="F69" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G69" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -2875,10 +2881,10 @@
         <v>6033.09</v>
       </c>
       <c r="F70" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G70" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -2904,10 +2910,10 @@
         <v>821332</v>
       </c>
       <c r="F71" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G71" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -2933,10 +2939,10 @@
         <v>216372.5</v>
       </c>
       <c r="F72" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G72" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -2962,10 +2968,10 @@
         <v>1449388.82</v>
       </c>
       <c r="F73" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G73" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -2991,10 +2997,10 @@
         <v>356426.52</v>
       </c>
       <c r="F74" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G74" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -3020,10 +3026,10 @@
         <v>794039.4</v>
       </c>
       <c r="F75" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G75" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -3049,10 +3055,10 @@
         <v>13344.75</v>
       </c>
       <c r="F76" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G76" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -3078,10 +3084,10 @@
         <v>1827028.29</v>
       </c>
       <c r="F77" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G77" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -3107,10 +3113,10 @@
         <v>1053</v>
       </c>
       <c r="F78" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G78" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -3136,10 +3142,10 @@
         <v>9146.1</v>
       </c>
       <c r="F79" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G79" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -3165,10 +3171,10 @@
         <v>1073676.99</v>
       </c>
       <c r="F80" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G80" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -3194,10 +3200,10 @@
         <v>3020872</v>
       </c>
       <c r="F81" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G81" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H81">
         <v>0.7685</v>
@@ -3223,10 +3229,10 @@
         <v>11430.75</v>
       </c>
       <c r="F82" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G82" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -3252,10 +3258,10 @@
         <v>33300</v>
       </c>
       <c r="F83" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G83" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -3281,10 +3287,10 @@
         <v>14073.68</v>
       </c>
       <c r="F84" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G84" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -3310,10 +3316,10 @@
         <v>16797004.83</v>
       </c>
       <c r="F85" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G85" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -3339,10 +3345,10 @@
         <v>15972</v>
       </c>
       <c r="F86" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G86" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -3368,10 +3374,10 @@
         <v>4702737</v>
       </c>
       <c r="F87" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G87" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -3397,10 +3403,10 @@
         <v>23104.65</v>
       </c>
       <c r="F88" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G88" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -3426,10 +3432,10 @@
         <v>17979638.16</v>
       </c>
       <c r="F89" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G89" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -3455,10 +3461,10 @@
         <v>676140</v>
       </c>
       <c r="F90" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G90" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -3484,10 +3490,10 @@
         <v>6771005</v>
       </c>
       <c r="F91" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G91" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H91">
         <v>0.7685</v>
@@ -3513,10 +3519,10 @@
         <v>1394.85</v>
       </c>
       <c r="F92" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G92" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -3542,10 +3548,10 @@
         <v>2309525.07</v>
       </c>
       <c r="F93" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G93" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -3571,10 +3577,10 @@
         <v>2359142.25</v>
       </c>
       <c r="F94" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G94" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -3600,10 +3606,10 @@
         <v>189509.2</v>
       </c>
       <c r="F95" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G95" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -3629,10 +3635,10 @@
         <v>955000</v>
       </c>
       <c r="F96" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G96" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -3658,10 +3664,10 @@
         <v>2374042</v>
       </c>
       <c r="F97" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G97" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -3687,10 +3693,10 @@
         <v>689076.42</v>
       </c>
       <c r="F98" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G98" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -3716,10 +3722,10 @@
         <v>3353024.4</v>
       </c>
       <c r="F99" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G99" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -3745,10 +3751,10 @@
         <v>10168344</v>
       </c>
       <c r="F100" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G100" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -3762,28 +3768,28 @@
         <v>89</v>
       </c>
       <c r="B101">
-        <v>5025</v>
+        <v>316025</v>
       </c>
       <c r="C101">
         <v>21.18</v>
       </c>
       <c r="D101">
-        <v>25.12</v>
+        <v>1580.12</v>
       </c>
       <c r="E101">
-        <v>106429.5</v>
+        <v>6693409.5</v>
       </c>
       <c r="F101" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G101" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H101">
         <v>1</v>
       </c>
       <c r="I101">
-        <v>106429.5</v>
+        <v>6693409.5</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -3791,28 +3797,28 @@
         <v>90</v>
       </c>
       <c r="B102">
-        <v>110000</v>
+        <v>193065</v>
       </c>
       <c r="C102">
-        <v>96.69</v>
+        <v>25.47</v>
       </c>
       <c r="D102">
-        <v>-595.96</v>
+        <v>9653.25</v>
       </c>
       <c r="E102">
-        <v>10635900</v>
+        <v>4917365.55</v>
       </c>
       <c r="F102" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G102" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H102">
         <v>1</v>
       </c>
       <c r="I102">
-        <v>10635900</v>
+        <v>4917365.55</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -3820,28 +3826,28 @@
         <v>91</v>
       </c>
       <c r="B103">
-        <v>293578</v>
+        <v>110000</v>
       </c>
       <c r="C103">
-        <v>42.76</v>
+        <v>96.69</v>
       </c>
       <c r="D103">
-        <v>4732.62</v>
+        <v>-595.96</v>
       </c>
       <c r="E103">
-        <v>12553395.28</v>
+        <v>10635900</v>
       </c>
       <c r="F103" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G103" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H103">
         <v>1</v>
       </c>
       <c r="I103">
-        <v>12553395.28</v>
+        <v>10635900</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -3849,28 +3855,28 @@
         <v>92</v>
       </c>
       <c r="B104">
-        <v>169600</v>
+        <v>112925</v>
       </c>
       <c r="C104">
-        <v>89.56999999999999</v>
+        <v>100.46</v>
       </c>
       <c r="D104">
-        <v>-29969.33</v>
+        <v>3387.75</v>
       </c>
       <c r="E104">
-        <v>15191072</v>
+        <v>11344445.5</v>
       </c>
       <c r="F104" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G104" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="H104">
         <v>1</v>
       </c>
       <c r="I104">
-        <v>15191072</v>
+        <v>11344445.5</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -3878,28 +3884,28 @@
         <v>93</v>
       </c>
       <c r="B105">
-        <v>25400</v>
+        <v>293578</v>
       </c>
       <c r="C105">
-        <v>79.34999999999999</v>
+        <v>42.76</v>
       </c>
       <c r="D105">
-        <v>38354</v>
+        <v>4732.62</v>
       </c>
       <c r="E105">
-        <v>2015490</v>
+        <v>12553395.28</v>
       </c>
       <c r="F105" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G105" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H105">
         <v>1</v>
       </c>
       <c r="I105">
-        <v>2015490</v>
+        <v>12553395.28</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -3907,28 +3913,28 @@
         <v>94</v>
       </c>
       <c r="B106">
-        <v>50000</v>
+        <v>169600</v>
       </c>
       <c r="C106">
-        <v>72.55</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="D106">
-        <v>89500</v>
+        <v>-29969.33</v>
       </c>
       <c r="E106">
-        <v>3627500</v>
+        <v>15191072</v>
       </c>
       <c r="F106" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G106" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H106">
         <v>1</v>
       </c>
       <c r="I106">
-        <v>3627500</v>
+        <v>15191072</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -3936,28 +3942,28 @@
         <v>95</v>
       </c>
       <c r="B107">
-        <v>44035</v>
+        <v>25400</v>
       </c>
       <c r="C107">
-        <v>39.92</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="D107">
-        <v>10568.4</v>
+        <v>38354</v>
       </c>
       <c r="E107">
-        <v>1757877.2</v>
+        <v>2015490</v>
       </c>
       <c r="F107" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G107" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H107">
         <v>1</v>
       </c>
       <c r="I107">
-        <v>1757877.2</v>
+        <v>2015490</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -3965,28 +3971,28 @@
         <v>96</v>
       </c>
       <c r="B108">
-        <v>27331</v>
+        <v>50000</v>
       </c>
       <c r="C108">
-        <v>58.88</v>
+        <v>72.55</v>
       </c>
       <c r="D108">
-        <v>44276.22</v>
+        <v>89500</v>
       </c>
       <c r="E108">
-        <v>1609249.28</v>
+        <v>3627500</v>
       </c>
       <c r="F108" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G108" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H108">
         <v>1</v>
       </c>
       <c r="I108">
-        <v>1609249.28</v>
+        <v>3627500</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -3994,28 +4000,28 @@
         <v>97</v>
       </c>
       <c r="B109">
-        <v>26700</v>
+        <v>44035</v>
       </c>
       <c r="C109">
-        <v>47.82</v>
+        <v>39.92</v>
       </c>
       <c r="D109">
-        <v>18156</v>
+        <v>10568.4</v>
       </c>
       <c r="E109">
-        <v>1276794</v>
+        <v>1757877.2</v>
       </c>
       <c r="F109" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G109" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H109">
         <v>1</v>
       </c>
       <c r="I109">
-        <v>1276794</v>
+        <v>1757877.2</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -4023,28 +4029,28 @@
         <v>98</v>
       </c>
       <c r="B110">
-        <v>14556</v>
+        <v>27331</v>
       </c>
       <c r="C110">
-        <v>83.59999999999999</v>
+        <v>58.88</v>
       </c>
       <c r="D110">
-        <v>17321.64</v>
+        <v>44276.22</v>
       </c>
       <c r="E110">
-        <v>1216881.6</v>
+        <v>1609249.28</v>
       </c>
       <c r="F110" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G110" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H110">
         <v>1</v>
       </c>
       <c r="I110">
-        <v>1216881.6</v>
+        <v>1609249.28</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -4052,28 +4058,28 @@
         <v>99</v>
       </c>
       <c r="B111">
-        <v>24400</v>
+        <v>26700</v>
       </c>
       <c r="C111">
-        <v>89.54000000000001</v>
+        <v>47.82</v>
       </c>
       <c r="D111">
-        <v>21245.45</v>
+        <v>18156</v>
       </c>
       <c r="E111">
-        <v>2184776</v>
+        <v>1276794</v>
       </c>
       <c r="F111" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G111" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H111">
         <v>1</v>
       </c>
       <c r="I111">
-        <v>2184776</v>
+        <v>1276794</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -4081,28 +4087,28 @@
         <v>100</v>
       </c>
       <c r="B112">
-        <v>-8610</v>
+        <v>14556</v>
       </c>
       <c r="C112">
-        <v>106.665</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D112">
-        <v>1140.5</v>
+        <v>17321.64</v>
       </c>
       <c r="E112">
-        <v>-918385.65</v>
+        <v>1216881.6</v>
       </c>
       <c r="F112" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G112" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H112">
         <v>1</v>
       </c>
       <c r="I112">
-        <v>-918385.65</v>
+        <v>1216881.6</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -4110,28 +4116,28 @@
         <v>101</v>
       </c>
       <c r="B113">
-        <v>53604</v>
+        <v>24400</v>
       </c>
       <c r="C113">
-        <v>109.89</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="D113">
-        <v>8040.6</v>
+        <v>21245.45</v>
       </c>
       <c r="E113">
-        <v>5890543.56</v>
+        <v>2184776</v>
       </c>
       <c r="F113" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G113" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H113">
         <v>1</v>
       </c>
       <c r="I113">
-        <v>5890543.56</v>
+        <v>2184776</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -4139,28 +4145,28 @@
         <v>102</v>
       </c>
       <c r="B114">
-        <v>200</v>
+        <v>-8610</v>
       </c>
       <c r="C114">
-        <v>59.94</v>
+        <v>106.665</v>
       </c>
       <c r="D114">
-        <v>-34</v>
+        <v>1140.5</v>
       </c>
       <c r="E114">
-        <v>11988</v>
+        <v>-918385.65</v>
       </c>
       <c r="F114" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G114" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H114">
         <v>1</v>
       </c>
       <c r="I114">
-        <v>11988</v>
+        <v>-918385.65</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -4168,28 +4174,28 @@
         <v>103</v>
       </c>
       <c r="B115">
-        <v>-50</v>
+        <v>53604</v>
       </c>
       <c r="C115">
-        <v>35.76</v>
+        <v>109.89</v>
       </c>
       <c r="D115">
-        <v>-1118.65</v>
+        <v>8040.6</v>
       </c>
       <c r="E115">
-        <v>-1788</v>
+        <v>5890543.56</v>
       </c>
       <c r="F115" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G115" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H115">
-        <v>0.1286</v>
+        <v>1</v>
       </c>
       <c r="I115">
-        <v>-229.94</v>
+        <v>5890543.56</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -4197,28 +4203,28 @@
         <v>104</v>
       </c>
       <c r="B116">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="C116">
-        <v>33.82</v>
+        <v>59.94</v>
       </c>
       <c r="D116">
-        <v>-1902.98</v>
+        <v>-34</v>
       </c>
       <c r="E116">
-        <v>1691</v>
+        <v>11988</v>
       </c>
       <c r="F116" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="G116" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H116">
-        <v>0.1286</v>
+        <v>1</v>
       </c>
       <c r="I116">
-        <v>217.46</v>
+        <v>11988</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -4226,28 +4232,28 @@
         <v>105</v>
       </c>
       <c r="B117">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="C117">
-        <v>48.87</v>
+        <v>35.76</v>
       </c>
       <c r="D117">
-        <v>-3651.67</v>
+        <v>-1118.65</v>
       </c>
       <c r="E117">
-        <v>-4887</v>
+        <v>-1788</v>
       </c>
       <c r="F117" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G117" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H117">
         <v>0.1286</v>
       </c>
       <c r="I117">
-        <v>-628.47</v>
+        <v>-229.94</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -4255,28 +4261,28 @@
         <v>106</v>
       </c>
       <c r="B118">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="C118">
-        <v>35.22</v>
+        <v>33.82</v>
       </c>
       <c r="D118">
-        <v>-2083</v>
+        <v>-1902.98</v>
       </c>
       <c r="E118">
-        <v>3522</v>
+        <v>1691</v>
       </c>
       <c r="F118" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G118" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H118">
         <v>0.1286</v>
       </c>
       <c r="I118">
-        <v>452.93</v>
+        <v>217.46</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -4284,28 +4290,28 @@
         <v>107</v>
       </c>
       <c r="B119">
-        <v>-8</v>
+        <v>-100</v>
       </c>
       <c r="C119">
-        <v>89.8034</v>
+        <v>48.87</v>
       </c>
       <c r="D119">
-        <v>-1541.2</v>
+        <v>-3651.67</v>
       </c>
       <c r="E119">
-        <v>-718.4299999999999</v>
+        <v>-4887</v>
       </c>
       <c r="F119" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G119" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H119">
-        <v>1</v>
+        <v>0.1286</v>
       </c>
       <c r="I119">
-        <v>-718.4299999999999</v>
+        <v>-628.47</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -4313,28 +4319,28 @@
         <v>108</v>
       </c>
       <c r="B120">
-        <v>-2</v>
+        <v>100</v>
       </c>
       <c r="C120">
-        <v>93.60039999999999</v>
+        <v>35.22</v>
       </c>
       <c r="D120">
-        <v>-411.6</v>
+        <v>-2083</v>
       </c>
       <c r="E120">
-        <v>-187.2</v>
+        <v>3522</v>
       </c>
       <c r="F120" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G120" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H120">
-        <v>1</v>
+        <v>0.1286</v>
       </c>
       <c r="I120">
-        <v>-187.2</v>
+        <v>452.93</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -4342,28 +4348,28 @@
         <v>109</v>
       </c>
       <c r="B121">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C121">
-        <v>115.1</v>
+        <v>89.8034</v>
       </c>
       <c r="D121">
-        <v>-2506.6</v>
+        <v>-1541.2</v>
       </c>
       <c r="E121">
-        <v>-1151</v>
+        <v>-718.4299999999999</v>
       </c>
       <c r="F121" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G121" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H121">
         <v>1</v>
       </c>
       <c r="I121">
-        <v>-1151</v>
+        <v>-718.4299999999999</v>
       </c>
     </row>
     <row r="122" spans="1:9">
@@ -4371,28 +4377,28 @@
         <v>110</v>
       </c>
       <c r="B122">
-        <v>8</v>
+        <v>-2</v>
       </c>
       <c r="C122">
-        <v>137.0245</v>
+        <v>93.60039999999999</v>
       </c>
       <c r="D122">
-        <v>-1387.36</v>
+        <v>-411.6</v>
       </c>
       <c r="E122">
-        <v>1096.2</v>
+        <v>-187.2</v>
       </c>
       <c r="F122" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G122" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H122">
         <v>1</v>
       </c>
       <c r="I122">
-        <v>1096.2</v>
+        <v>-187.2</v>
       </c>
     </row>
     <row r="123" spans="1:9">
@@ -4400,28 +4406,28 @@
         <v>111</v>
       </c>
       <c r="B123">
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="C123">
-        <v>144.918</v>
+        <v>115.1</v>
       </c>
       <c r="D123">
-        <v>-2668.48</v>
+        <v>-2506.6</v>
       </c>
       <c r="E123">
-        <v>-1159.34</v>
+        <v>-1151</v>
       </c>
       <c r="F123" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G123" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H123">
         <v>1</v>
       </c>
       <c r="I123">
-        <v>-1159.34</v>
+        <v>-1151</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -4429,28 +4435,28 @@
         <v>112</v>
       </c>
       <c r="B124">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C124">
-        <v>108.9736</v>
+        <v>137.0245</v>
       </c>
       <c r="D124">
-        <v>-1009.95</v>
+        <v>-1387.36</v>
       </c>
       <c r="E124">
-        <v>544.87</v>
+        <v>1096.2</v>
       </c>
       <c r="F124" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G124" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H124">
         <v>1</v>
       </c>
       <c r="I124">
-        <v>544.87</v>
+        <v>1096.2</v>
       </c>
     </row>
     <row r="125" spans="1:9">
@@ -4458,28 +4464,28 @@
         <v>113</v>
       </c>
       <c r="B125">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="C125">
-        <v>27.2485</v>
+        <v>144.918</v>
       </c>
       <c r="D125">
-        <v>176.2</v>
+        <v>-2668.48</v>
       </c>
       <c r="E125">
-        <v>-272.48</v>
+        <v>-1159.34</v>
       </c>
       <c r="F125" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G125" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H125">
         <v>1</v>
       </c>
       <c r="I125">
-        <v>-272.48</v>
+        <v>-1159.34</v>
       </c>
     </row>
     <row r="126" spans="1:9">
@@ -4487,28 +4493,28 @@
         <v>114</v>
       </c>
       <c r="B126">
-        <v>-30</v>
+        <v>5</v>
       </c>
       <c r="C126">
-        <v>39.5124</v>
+        <v>108.9736</v>
       </c>
       <c r="D126">
-        <v>275.4</v>
+        <v>-1009.95</v>
       </c>
       <c r="E126">
-        <v>-1185.37</v>
+        <v>544.87</v>
       </c>
       <c r="F126" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G126" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H126">
         <v>1</v>
       </c>
       <c r="I126">
-        <v>-1185.37</v>
+        <v>544.87</v>
       </c>
     </row>
     <row r="127" spans="1:9">
@@ -4516,28 +4522,28 @@
         <v>115</v>
       </c>
       <c r="B127">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="C127">
-        <v>49.4728</v>
+        <v>27.2485</v>
       </c>
       <c r="D127">
-        <v>665.4</v>
+        <v>176.2</v>
       </c>
       <c r="E127">
-        <v>742.09</v>
+        <v>-272.48</v>
       </c>
       <c r="F127" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G127" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H127">
         <v>1</v>
       </c>
       <c r="I127">
-        <v>742.09</v>
+        <v>-272.48</v>
       </c>
     </row>
     <row r="128" spans="1:9">
@@ -4545,28 +4551,28 @@
         <v>116</v>
       </c>
       <c r="B128">
-        <v>-15</v>
+        <v>-30</v>
       </c>
       <c r="C128">
-        <v>43.708</v>
+        <v>39.5124</v>
       </c>
       <c r="D128">
-        <v>78.15000000000001</v>
+        <v>275.4</v>
       </c>
       <c r="E128">
-        <v>-655.62</v>
+        <v>-1185.37</v>
       </c>
       <c r="F128" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G128" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H128">
         <v>1</v>
       </c>
       <c r="I128">
-        <v>-655.62</v>
+        <v>-1185.37</v>
       </c>
     </row>
     <row r="129" spans="1:9">
@@ -4574,28 +4580,28 @@
         <v>117</v>
       </c>
       <c r="B129">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C129">
-        <v>44.7384</v>
+        <v>49.4728</v>
       </c>
       <c r="D129">
-        <v>148.1</v>
+        <v>665.4</v>
       </c>
       <c r="E129">
-        <v>447.38</v>
+        <v>742.09</v>
       </c>
       <c r="F129" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G129" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H129">
         <v>1</v>
       </c>
       <c r="I129">
-        <v>447.38</v>
+        <v>742.09</v>
       </c>
     </row>
     <row r="130" spans="1:9">
@@ -4603,28 +4609,28 @@
         <v>118</v>
       </c>
       <c r="B130">
-        <v>-30</v>
+        <v>-15</v>
       </c>
       <c r="C130">
-        <v>48.54</v>
+        <v>43.708</v>
       </c>
       <c r="D130">
-        <v>1054.5</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="E130">
-        <v>-1456.2</v>
+        <v>-655.62</v>
       </c>
       <c r="F130" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G130" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H130">
         <v>1</v>
       </c>
       <c r="I130">
-        <v>-1456.2</v>
+        <v>-655.62</v>
       </c>
     </row>
     <row r="131" spans="1:9">
@@ -4632,28 +4638,28 @@
         <v>119</v>
       </c>
       <c r="B131">
-        <v>-15</v>
+        <v>10</v>
       </c>
       <c r="C131">
-        <v>65.7372</v>
+        <v>44.7384</v>
       </c>
       <c r="D131">
-        <v>56.85</v>
+        <v>148.1</v>
       </c>
       <c r="E131">
-        <v>-986.0599999999999</v>
+        <v>447.38</v>
       </c>
       <c r="F131" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G131" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H131">
         <v>1</v>
       </c>
       <c r="I131">
-        <v>-986.0599999999999</v>
+        <v>447.38</v>
       </c>
     </row>
     <row r="132" spans="1:9">
@@ -4661,28 +4667,28 @@
         <v>120</v>
       </c>
       <c r="B132">
-        <v>20</v>
+        <v>-30</v>
       </c>
       <c r="C132">
-        <v>9.66</v>
+        <v>48.54</v>
       </c>
       <c r="D132">
-        <v>2169.8</v>
+        <v>1054.5</v>
       </c>
       <c r="E132">
-        <v>193.2</v>
+        <v>-1456.2</v>
       </c>
       <c r="F132" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G132" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H132">
         <v>1</v>
       </c>
       <c r="I132">
-        <v>193.2</v>
+        <v>-1456.2</v>
       </c>
     </row>
     <row r="133" spans="1:9">
@@ -4690,28 +4696,28 @@
         <v>121</v>
       </c>
       <c r="B133">
-        <v>-25</v>
+        <v>-15</v>
       </c>
       <c r="C133">
-        <v>1168</v>
+        <v>65.7372</v>
       </c>
       <c r="D133">
-        <v>38500</v>
+        <v>56.85</v>
       </c>
       <c r="E133">
-        <v>-29200</v>
+        <v>-986.0599999999999</v>
       </c>
       <c r="F133" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G133" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H133">
         <v>1</v>
       </c>
       <c r="I133">
-        <v>-29200</v>
+        <v>-986.0599999999999</v>
       </c>
     </row>
     <row r="134" spans="1:9">
@@ -4719,28 +4725,28 @@
         <v>122</v>
       </c>
       <c r="B134">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C134">
-        <v>446.5</v>
+        <v>9.66</v>
       </c>
       <c r="D134">
-        <v>-27625</v>
+        <v>2169.8</v>
       </c>
       <c r="E134">
-        <v>11162.5</v>
+        <v>193.2</v>
       </c>
       <c r="F134" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G134" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H134">
         <v>1</v>
       </c>
       <c r="I134">
-        <v>11162.5</v>
+        <v>193.2</v>
       </c>
     </row>
     <row r="135" spans="1:9">
@@ -4748,28 +4754,28 @@
         <v>123</v>
       </c>
       <c r="B135">
-        <v>10</v>
+        <v>-25</v>
       </c>
       <c r="C135">
-        <v>94.07550000000001</v>
+        <v>1168</v>
       </c>
       <c r="D135">
-        <v>-3470.8</v>
+        <v>38500</v>
       </c>
       <c r="E135">
-        <v>940.76</v>
+        <v>-29200</v>
       </c>
       <c r="F135" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G135" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H135">
         <v>1</v>
       </c>
       <c r="I135">
-        <v>940.76</v>
+        <v>-29200</v>
       </c>
     </row>
     <row r="136" spans="1:9">
@@ -4777,28 +4783,28 @@
         <v>124</v>
       </c>
       <c r="B136">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="C136">
-        <v>111.2551</v>
+        <v>446.5</v>
       </c>
       <c r="D136">
-        <v>-5051.2</v>
+        <v>-27625</v>
       </c>
       <c r="E136">
-        <v>-2225.1</v>
+        <v>11162.5</v>
       </c>
       <c r="F136" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G136" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H136">
         <v>1</v>
       </c>
       <c r="I136">
-        <v>-2225.1</v>
+        <v>11162.5</v>
       </c>
     </row>
     <row r="137" spans="1:9">
@@ -4806,28 +4812,28 @@
         <v>125</v>
       </c>
       <c r="B137">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C137">
-        <v>42.3717</v>
+        <v>94.07550000000001</v>
       </c>
       <c r="D137">
-        <v>5762.88</v>
+        <v>-3470.8</v>
       </c>
       <c r="E137">
-        <v>1016.92</v>
+        <v>940.76</v>
       </c>
       <c r="F137" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G137" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H137">
         <v>1</v>
       </c>
       <c r="I137">
-        <v>1016.92</v>
+        <v>940.76</v>
       </c>
     </row>
     <row r="138" spans="1:9">
@@ -4835,28 +4841,28 @@
         <v>126</v>
       </c>
       <c r="B138">
-        <v>-48</v>
+        <v>-20</v>
       </c>
       <c r="C138">
-        <v>41.4835</v>
+        <v>111.2551</v>
       </c>
       <c r="D138">
-        <v>12024.48</v>
+        <v>-5051.2</v>
       </c>
       <c r="E138">
-        <v>-1991.21</v>
+        <v>-2225.1</v>
       </c>
       <c r="F138" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G138" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H138">
         <v>1</v>
       </c>
       <c r="I138">
-        <v>-1991.21</v>
+        <v>-2225.1</v>
       </c>
     </row>
     <row r="139" spans="1:9">
@@ -4864,28 +4870,28 @@
         <v>127</v>
       </c>
       <c r="B139">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C139">
-        <v>74.0128</v>
+        <v>42.3717</v>
       </c>
       <c r="D139">
-        <v>4119.24</v>
+        <v>5762.88</v>
       </c>
       <c r="E139">
-        <v>888.15</v>
+        <v>1016.92</v>
       </c>
       <c r="F139" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G139" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H139">
         <v>1</v>
       </c>
       <c r="I139">
-        <v>888.15</v>
+        <v>1016.92</v>
       </c>
     </row>
     <row r="140" spans="1:9">
@@ -4893,28 +4899,28 @@
         <v>128</v>
       </c>
       <c r="B140">
-        <v>-1200</v>
+        <v>-48</v>
       </c>
       <c r="C140">
-        <v>6.1503</v>
+        <v>41.4835</v>
       </c>
       <c r="D140">
-        <v>-111108</v>
+        <v>12024.48</v>
       </c>
       <c r="E140">
-        <v>-7380.36</v>
+        <v>-1991.21</v>
       </c>
       <c r="F140" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G140" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H140">
         <v>1</v>
       </c>
       <c r="I140">
-        <v>-7380.36</v>
+        <v>-1991.21</v>
       </c>
     </row>
     <row r="141" spans="1:9">
@@ -4922,28 +4928,28 @@
         <v>129</v>
       </c>
       <c r="B141">
-        <v>200</v>
+        <v>12</v>
       </c>
       <c r="C141">
-        <v>1.7208</v>
+        <v>74.0128</v>
       </c>
       <c r="D141">
-        <v>-5532</v>
+        <v>4119.24</v>
       </c>
       <c r="E141">
-        <v>344.16</v>
+        <v>888.15</v>
       </c>
       <c r="F141" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G141" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H141">
         <v>1</v>
       </c>
       <c r="I141">
-        <v>344.16</v>
+        <v>888.15</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -4951,28 +4957,28 @@
         <v>130</v>
       </c>
       <c r="B142">
-        <v>100</v>
+        <v>-1200</v>
       </c>
       <c r="C142">
-        <v>1.295</v>
+        <v>6.1503</v>
       </c>
       <c r="D142">
-        <v>-1397</v>
+        <v>-111108</v>
       </c>
       <c r="E142">
-        <v>129.5</v>
+        <v>-7380.36</v>
       </c>
       <c r="F142" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G142" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H142">
         <v>1</v>
       </c>
       <c r="I142">
-        <v>129.5</v>
+        <v>-7380.36</v>
       </c>
     </row>
     <row r="143" spans="1:9">
@@ -4980,28 +4986,28 @@
         <v>131</v>
       </c>
       <c r="B143">
-        <v>-800</v>
+        <v>200</v>
       </c>
       <c r="C143">
-        <v>66.0466</v>
+        <v>1.7208</v>
       </c>
       <c r="D143">
-        <v>150568</v>
+        <v>-5532</v>
       </c>
       <c r="E143">
-        <v>-52837.28</v>
+        <v>344.16</v>
       </c>
       <c r="F143" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G143" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H143">
         <v>1</v>
       </c>
       <c r="I143">
-        <v>-52837.28</v>
+        <v>344.16</v>
       </c>
     </row>
     <row r="144" spans="1:9">
@@ -5009,28 +5015,28 @@
         <v>132</v>
       </c>
       <c r="B144">
-        <v>-500</v>
+        <v>100</v>
       </c>
       <c r="C144">
-        <v>65.16800000000001</v>
+        <v>1.295</v>
       </c>
       <c r="D144">
-        <v>94215</v>
+        <v>-1397</v>
       </c>
       <c r="E144">
-        <v>-32584</v>
+        <v>129.5</v>
       </c>
       <c r="F144" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G144" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H144">
         <v>1</v>
       </c>
       <c r="I144">
-        <v>-32584</v>
+        <v>129.5</v>
       </c>
     </row>
     <row r="145" spans="1:9">
@@ -5038,28 +5044,28 @@
         <v>133</v>
       </c>
       <c r="B145">
-        <v>1300</v>
+        <v>-800</v>
       </c>
       <c r="C145">
-        <v>42.7131</v>
+        <v>66.0466</v>
       </c>
       <c r="D145">
-        <v>-237016</v>
+        <v>150568</v>
       </c>
       <c r="E145">
-        <v>55527.03</v>
+        <v>-52837.28</v>
       </c>
       <c r="F145" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G145" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H145">
         <v>1</v>
       </c>
       <c r="I145">
-        <v>55527.03</v>
+        <v>-52837.28</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -5067,28 +5073,28 @@
         <v>134</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="C146">
-        <v>23.6576</v>
+        <v>65.16800000000001</v>
       </c>
       <c r="D146">
-        <v>244150.8</v>
+        <v>94215</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>-32584</v>
       </c>
       <c r="F146" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G146" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H146">
         <v>1</v>
       </c>
       <c r="I146">
-        <v>0</v>
+        <v>-32584</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -5096,28 +5102,28 @@
         <v>135</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="C147">
-        <v>9.02</v>
+        <v>42.7131</v>
       </c>
       <c r="D147">
-        <v>-134230.6</v>
+        <v>-237016</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>55527.03</v>
       </c>
       <c r="F147" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G147" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H147">
         <v>1</v>
       </c>
       <c r="I147">
-        <v>0</v>
+        <v>55527.03</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -5125,28 +5131,28 @@
         <v>136</v>
       </c>
       <c r="B148">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>19.1405</v>
+        <v>23.6576</v>
       </c>
       <c r="D148">
-        <v>-1000.5</v>
+        <v>244150.8</v>
       </c>
       <c r="E148">
-        <v>-957.02</v>
+        <v>0</v>
       </c>
       <c r="F148" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G148" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H148">
         <v>1</v>
       </c>
       <c r="I148">
-        <v>-957.02</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -5154,28 +5160,28 @@
         <v>137</v>
       </c>
       <c r="B149">
-        <v>-236</v>
+        <v>0</v>
       </c>
       <c r="C149">
-        <v>20.986</v>
+        <v>9.02</v>
       </c>
       <c r="D149">
-        <v>-4984.32</v>
+        <v>-134230.6</v>
       </c>
       <c r="E149">
-        <v>-4952.7</v>
+        <v>0</v>
       </c>
       <c r="F149" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G149" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H149">
         <v>1</v>
       </c>
       <c r="I149">
-        <v>-4952.7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -5183,28 +5189,28 @@
         <v>138</v>
       </c>
       <c r="B150">
-        <v>-140</v>
+        <v>-50</v>
       </c>
       <c r="C150">
-        <v>21.9283</v>
+        <v>19.1405</v>
       </c>
       <c r="D150">
-        <v>-3161.2</v>
+        <v>-1000.5</v>
       </c>
       <c r="E150">
-        <v>-3069.96</v>
+        <v>-957.02</v>
       </c>
       <c r="F150" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G150" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H150">
         <v>1</v>
       </c>
       <c r="I150">
-        <v>-3069.96</v>
+        <v>-957.02</v>
       </c>
     </row>
     <row r="151" spans="1:9">
@@ -5212,28 +5218,28 @@
         <v>139</v>
       </c>
       <c r="B151">
-        <v>-1</v>
+        <v>-236</v>
       </c>
       <c r="C151">
-        <v>55.43</v>
+        <v>20.986</v>
       </c>
       <c r="D151">
-        <v>-19</v>
+        <v>-4984.32</v>
       </c>
       <c r="E151">
-        <v>-55.43</v>
+        <v>-4952.7</v>
       </c>
       <c r="F151" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G151" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H151">
         <v>1</v>
       </c>
       <c r="I151">
-        <v>-55.43</v>
+        <v>-4952.7</v>
       </c>
     </row>
     <row r="152" spans="1:9">
@@ -5241,28 +5247,28 @@
         <v>140</v>
       </c>
       <c r="B152">
-        <v>48</v>
+        <v>-140</v>
       </c>
       <c r="C152">
-        <v>29.7274</v>
+        <v>21.9283</v>
       </c>
       <c r="D152">
-        <v>-928.8</v>
+        <v>-3161.2</v>
       </c>
       <c r="E152">
-        <v>1426.92</v>
+        <v>-3069.96</v>
       </c>
       <c r="F152" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G152" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H152">
         <v>1</v>
       </c>
       <c r="I152">
-        <v>1426.92</v>
+        <v>-3069.96</v>
       </c>
     </row>
     <row r="153" spans="1:9">
@@ -5270,28 +5276,28 @@
         <v>141</v>
       </c>
       <c r="B153">
-        <v>60</v>
+        <v>-1</v>
       </c>
       <c r="C153">
-        <v>24.746</v>
+        <v>55.43</v>
       </c>
       <c r="D153">
-        <v>-1218</v>
+        <v>-19</v>
       </c>
       <c r="E153">
-        <v>1484.76</v>
+        <v>-55.43</v>
       </c>
       <c r="F153" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G153" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H153">
         <v>1</v>
       </c>
       <c r="I153">
-        <v>1484.76</v>
+        <v>-55.43</v>
       </c>
     </row>
     <row r="154" spans="1:9">
@@ -5299,28 +5305,28 @@
         <v>142</v>
       </c>
       <c r="B154">
-        <v>108</v>
+        <v>48</v>
       </c>
       <c r="C154">
-        <v>19.8335</v>
+        <v>29.7274</v>
       </c>
       <c r="D154">
-        <v>-2473.2</v>
+        <v>-928.8</v>
       </c>
       <c r="E154">
-        <v>2142.02</v>
+        <v>1426.92</v>
       </c>
       <c r="F154" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G154" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H154">
         <v>1</v>
       </c>
       <c r="I154">
-        <v>2142.02</v>
+        <v>1426.92</v>
       </c>
     </row>
     <row r="155" spans="1:9">
@@ -5328,28 +5334,28 @@
         <v>143</v>
       </c>
       <c r="B155">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C155">
-        <v>7.4404</v>
+        <v>24.746</v>
       </c>
       <c r="D155">
-        <v>-963</v>
+        <v>-1218</v>
       </c>
       <c r="E155">
-        <v>372.02</v>
+        <v>1484.76</v>
       </c>
       <c r="F155" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G155" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H155">
         <v>1</v>
       </c>
       <c r="I155">
-        <v>372.02</v>
+        <v>1484.76</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -5357,28 +5363,28 @@
         <v>144</v>
       </c>
       <c r="B156">
-        <v>-60</v>
+        <v>108</v>
       </c>
       <c r="C156">
-        <v>143.35</v>
+        <v>19.8335</v>
       </c>
       <c r="D156">
-        <v>-2044.2</v>
+        <v>-2473.2</v>
       </c>
       <c r="E156">
-        <v>-8601</v>
+        <v>2142.02</v>
       </c>
       <c r="F156" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G156" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H156">
         <v>1</v>
       </c>
       <c r="I156">
-        <v>-8601</v>
+        <v>2142.02</v>
       </c>
     </row>
     <row r="157" spans="1:9">
@@ -5386,28 +5392,28 @@
         <v>145</v>
       </c>
       <c r="B157">
-        <v>-60</v>
+        <v>50</v>
       </c>
       <c r="C157">
-        <v>169.8521</v>
+        <v>7.4404</v>
       </c>
       <c r="D157">
-        <v>-3316.8</v>
+        <v>-963</v>
       </c>
       <c r="E157">
-        <v>-10191.13</v>
+        <v>372.02</v>
       </c>
       <c r="F157" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G157" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H157">
         <v>1</v>
       </c>
       <c r="I157">
-        <v>-10191.13</v>
+        <v>372.02</v>
       </c>
     </row>
     <row r="158" spans="1:9">
@@ -5415,28 +5421,28 @@
         <v>146</v>
       </c>
       <c r="B158">
-        <v>45</v>
+        <v>-60</v>
       </c>
       <c r="C158">
-        <v>103.7532</v>
+        <v>143.35</v>
       </c>
       <c r="D158">
-        <v>-9903.629999999999</v>
+        <v>-2044.2</v>
       </c>
       <c r="E158">
-        <v>4668.89</v>
+        <v>-8601</v>
       </c>
       <c r="F158" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G158" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H158">
         <v>1</v>
       </c>
       <c r="I158">
-        <v>4668.89</v>
+        <v>-8601</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -5447,25 +5453,25 @@
         <v>-60</v>
       </c>
       <c r="C159">
-        <v>117.725</v>
+        <v>169.8521</v>
       </c>
       <c r="D159">
-        <v>429.28</v>
+        <v>-3316.8</v>
       </c>
       <c r="E159">
-        <v>-7063.5</v>
+        <v>-10191.13</v>
       </c>
       <c r="F159" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G159" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H159">
         <v>1</v>
       </c>
       <c r="I159">
-        <v>-7063.5</v>
+        <v>-10191.13</v>
       </c>
     </row>
     <row r="160" spans="1:9">
@@ -5473,28 +5479,28 @@
         <v>148</v>
       </c>
       <c r="B160">
-        <v>-60</v>
+        <v>45</v>
       </c>
       <c r="C160">
-        <v>130.157</v>
+        <v>103.7532</v>
       </c>
       <c r="D160">
-        <v>237.28</v>
+        <v>-9903.629999999999</v>
       </c>
       <c r="E160">
-        <v>-7809.42</v>
+        <v>4668.89</v>
       </c>
       <c r="F160" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G160" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H160">
         <v>1</v>
       </c>
       <c r="I160">
-        <v>-7809.42</v>
+        <v>4668.89</v>
       </c>
     </row>
     <row r="161" spans="1:9">
@@ -5502,28 +5508,28 @@
         <v>149</v>
       </c>
       <c r="B161">
-        <v>45</v>
+        <v>-60</v>
       </c>
       <c r="C161">
-        <v>107.925</v>
+        <v>117.725</v>
       </c>
       <c r="D161">
-        <v>-5752.92</v>
+        <v>429.28</v>
       </c>
       <c r="E161">
-        <v>4856.62</v>
+        <v>-7063.5</v>
       </c>
       <c r="F161" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G161" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H161">
         <v>1</v>
       </c>
       <c r="I161">
-        <v>4856.62</v>
+        <v>-7063.5</v>
       </c>
     </row>
     <row r="162" spans="1:9">
@@ -5531,28 +5537,28 @@
         <v>150</v>
       </c>
       <c r="B162">
-        <v>-30</v>
+        <v>-60</v>
       </c>
       <c r="C162">
-        <v>46.6415</v>
+        <v>130.157</v>
       </c>
       <c r="D162">
-        <v>4927.5</v>
+        <v>237.28</v>
       </c>
       <c r="E162">
-        <v>-1399.24</v>
+        <v>-7809.42</v>
       </c>
       <c r="F162" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G162" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H162">
         <v>1</v>
       </c>
       <c r="I162">
-        <v>-1399.24</v>
+        <v>-7809.42</v>
       </c>
     </row>
     <row r="163" spans="1:9">
@@ -5560,27 +5566,85 @@
         <v>151</v>
       </c>
       <c r="B163">
+        <v>45</v>
+      </c>
+      <c r="C163">
+        <v>107.925</v>
+      </c>
+      <c r="D163">
+        <v>-5752.92</v>
+      </c>
+      <c r="E163">
+        <v>4856.62</v>
+      </c>
+      <c r="F163" t="s">
+        <v>157</v>
+      </c>
+      <c r="G163" t="s">
+        <v>162</v>
+      </c>
+      <c r="H163">
+        <v>1</v>
+      </c>
+      <c r="I163">
+        <v>4856.62</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9">
+      <c r="A164" t="s">
+        <v>152</v>
+      </c>
+      <c r="B164">
+        <v>-30</v>
+      </c>
+      <c r="C164">
+        <v>46.6415</v>
+      </c>
+      <c r="D164">
+        <v>4927.5</v>
+      </c>
+      <c r="E164">
+        <v>-1399.24</v>
+      </c>
+      <c r="F164" t="s">
+        <v>157</v>
+      </c>
+      <c r="G164" t="s">
+        <v>162</v>
+      </c>
+      <c r="H164">
+        <v>1</v>
+      </c>
+      <c r="I164">
+        <v>-1399.24</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9">
+      <c r="A165" t="s">
+        <v>153</v>
+      </c>
+      <c r="B165">
         <v>10</v>
       </c>
-      <c r="C163">
+      <c r="C165">
         <v>28.7</v>
       </c>
-      <c r="D163">
+      <c r="D165">
         <v>2450</v>
       </c>
-      <c r="E163">
+      <c r="E165">
         <v>287</v>
       </c>
-      <c r="F163" t="s">
-        <v>155</v>
-      </c>
-      <c r="G163" t="s">
-        <v>160</v>
-      </c>
-      <c r="H163">
-        <v>1</v>
-      </c>
-      <c r="I163">
+      <c r="F165" t="s">
+        <v>157</v>
+      </c>
+      <c r="G165" t="s">
+        <v>162</v>
+      </c>
+      <c r="H165">
+        <v>1</v>
+      </c>
+      <c r="I165">
         <v>287</v>
       </c>
     </row>
